--- a/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_05_20_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_05_20_Cau.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>60</v>
@@ -639,7 +639,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bắt đầu ngay trước lời gọi mạng và kết thúc ngay sau khi lời gọi trả về.</t>
+          <t>Để đo độ trễ thuần của lời gọi API, mốc thời gian bắt đầu `start=now()` phải đặt ngay trước lời gọi mạng `response=client.call(req)` và mốc kết thúc tính ngay sau khi lời gọi trả về `elapsed=now()-start`, không kèm bước nạp dữ liệu hay render.</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -685,7 +685,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thời gian trôi qua = thời điểm kết thúc − thời điểm bắt đầu.</t>
+          <t>Độ trễ thuần của lời gọi API = Thời điểm kết thúc − Thời điểm bắt đầu = 13,925 − 12,350 = 1,575 giây.</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C</t>
+          <t>1-B, 2-A, 3-C</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi instruction nào phải giữ nguyên qua nhiều task của user.</t>
+          <t>'Luôn trả lời như trợ giảng, không tiết lộ secret' (x1) là System content (r1); 'Hãy giải thích attention cho tôi bằng ví dụ' (x2) là User content (r2); 'System message phải xuất hiện trước user message' (x3) là Ràng buộc thứ tự, không phải nội dung yêu cầu của người học (r3).</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C, 4-D</t>
+          <t>1-C, 2-B, 3-D, 4-A</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi lớp trả lời một câu: model hành xử ra sao, user muốn gì, dùng dữ kiện nào và output phải có dạng gì.</t>
+          <t>'Bạn là chuyên viên phân tích...' (x1) là Chỉ dẫn system về cách model hành xử (r1); 'Câu hỏi: Vì sao doanh thu giảm?' (x2) là Input hiện tại của user (r2); 'Bảng doanh thu Q1–Q4' (x3) là Context hỗ trợ (r3); 'Trả JSON gồm cause và evidence_row' (x4) là Hợp đồng output (r4).</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C</t>
+          <t>1-A, 2-C, 3-B</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -965,7 +965,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách đường dẫn content khỏi hai trường thống kê token.</t>
+          <t>choices[0].message.content (x1) tương ứng với result.text (r1); usage.prompt_tokens (x2) tương ứng với metrics.input_tokens (r2); usage.completion_tokens (x3) tương ứng với metrics.output_tokens (r3).</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o4 → o1</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1017,7 +1017,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi kiểu dữ liệu: text → token ID/tensor → ID được sinh → text.</t>
+          <t>Quy trình suy luận causal language model cục bộ: Nạp tokenizer và causal LM tương thích (o2) -&gt; Tokenize/encode prompt thành tensor (o3) -&gt; Gọi generate với giới hạn output (o4) -&gt; Giải mã (decode) các token ID được sinh thành text (o1).</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1063,7 +1063,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Token ID chỉ có ý nghĩa trong vocabulary mà model đã được huấn luyện.</t>
+          <t>Nạp tokenizer của `model-A` nhưng nạp trọng số của `model-B` khi từ điển khác nhau sẽ dẫn đến việc các token ID bị ánh xạ sai lệch hoàn toàn hoặc vượt quá phạm vi embedding matrix của model, gây lỗi crash hoặc sinh rác.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1109,7 +1109,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt đối tượng truyền tải với từng phần dữ liệu nội dung.</t>
+          <t>Khi một hàm trả về stream (iterator các chunk/event) trong khi bên gọi cần chuỗi hoàn chỉnh, lỗi là iterator chưa được duyệt và các delta nội dung chưa được trích xuất để ghép nối lại thành một chuỗi text hoàn chỉnh.</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3</t>
+          <t>o2 → o3 → o1</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng số thứ tự, không dùng thứ tự các phần tử đến.</t>
+          <t>Khi các delta đến lệch thứ tự (3,'C'), (1,'A'), (2,'B'), hợp đồng yêu cầu phát theo số thứ tự: Thứ tự 1: A (o2) -&gt; Thứ tự 2: B (o3) -&gt; Thứ tự 3: C (o1).</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C</t>
+          <t>1-B, 2-C, 3-A</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1216,7 +1216,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi kết quả từng phần có an toàn và hữu ích trước khi hoàn tất hay không.</t>
+          <t>Cuộc trò chuyện dài, người dùng chấp nhận đọc dần (x1) dùng truyền kết quả từng phần streaming (r1); JSON phải kiểm tra toàn bộ trước khi hệ thống tài chính nhận (x2) cần giữ toàn bộ kết quả rồi kiểm tra trước khi chuyển tiếp (r2); Xử lý theo lô ở chế độ ngoại tuyến không người chờ (x3) dùng thu thập theo lô đơn giản (r3).</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1262,7 +1262,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ràng buộc quyết định là `trước khi hiển thị bất kỳ byte nào`.</t>
+          <t>Nếu ứng dụng có yêu cầu bắt buộc phải kiểm tra schema và chữ ký trên toàn bộ phản hồi trước khi hiển thị bất kỳ byte nào, chế độ phù hợp trực tiếp là không streaming hoặc phải đệm (buffer) toàn bộ response rồi mới hiển thị.</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o4 → o1</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1314,7 +1314,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi câu trả lời của assistant phải đứng sau lượt user mà nó trả lời.</t>
+          <t>Thứ tự hội thoại theo thời gian bắt đầu từ trạng thái rỗng là: user:U1 (o2) -&gt; assistant:A1 (o3) -&gt; user:U2 (o4) -&gt; assistant:A2 (o1).</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1367,7 +1367,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một policy tốt phải có quy tắc có thể kiểm thử và giữ trình tự cùng state cần thiết.</t>
+          <t>Các chính sách quản lý state hội thoại có kiểm soát gồm: Giữ N lượt gần nhất (sliding window) (a), Tóm tắt lượt cũ và giữ lượt gần đây (b), và Truy xuất state/fact liên quan theo ngữ cảnh (c). Xáo trộn hoặc xóa ngẫu nhiên làm hỏng tính mạch lạc.</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>1,2,5</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -1466,7 +1466,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ retry lỗi có khả năng tự thay đổi theo thời gian mà không cần sửa request hoặc credential.</t>
+          <t>Lỗi có thể retry là lỗi tạm thời có khả năng tự phục hồi: Timeout mạng tạm thời (a), Lỗi rate-limit 429 có Retry-After (b), và Lỗi 503 Service Unavailable tạm thời (e). Lỗi sai API key (c) và malformed schema (d) là lỗi 4xx cố định, không được retry.</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1519,7 +1519,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi người kiểm thử cần biết gì để quyết định phần triển khai đạt hay không.</t>
+          <t>Đặc tả kiểm thử được cần: Định dạng/kích thước file và xử lý lỗi (a), Luồng giao diện/API (b), Ràng buộc bảo mật và lưu trữ (c), cùng Tiêu chí chấp nhận kiểm thử được (d).</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1565,7 +1565,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một bài kiểm thử phải có thể trả kết quả đạt/không đạt từ hành vi cụ thể.</t>
+          <t>Tiêu chí chấp nhận kiểm thử được phải có đầu vào cụ thể, hành vi quan sát được và kết quả đạt/không đạt rõ ràng: 'Với CSV amount gồm 2, 3 và một dòng trống, hàm trả 5 và không gọi mạng'.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
@@ -1618,7 +1618,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn hành động tạo bằng chứng quan sát được về hành vi so với contract.</t>
+          <t>Bằng chứng kiểm chứng trực tiếp gồm: Đối chiếu tiêu chí chấp nhận với code/test (a), Chạy bộ test đường bình thường và test biên/đối nghịch (b), và Kiểm tra hậu quả lỗi cùng regression test (d). Tin tưởng vì mã trông trôi chảy (c) hay hỏi lại mô hình (e) không tạo bằng chứng kiểm thử khách quan.</t>
         </is>
       </c>
     </row>
